--- a/samples/Sample_3_For_International_Masters_College.xlsx
+++ b/samples/Sample_3_For_International_Masters_College.xlsx
@@ -1030,7 +1030,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Akash Sharma</t>
+          <t>Akash Shetty</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Tanya Kulkarni</t>
+          <t>Kavya Rao</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -1064,7 +1064,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Ishaan Desai</t>
+          <t>Nikhil Iyer</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Kavya Kulkarni</t>
+          <t>Ishita Sharma</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1098,7 +1098,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Vivaan Joshi</t>
+          <t>Vihaan Shetty</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1115,7 +1115,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Ananya Rao</t>
+          <t>Diya Iyer</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1132,7 +1132,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Rahul Naik</t>
+          <t>Sameer Naik</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1149,7 +1149,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Tanya Naik</t>
+          <t>Kavya Iyer</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1166,7 +1166,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Pranav Hegde</t>
+          <t>Arjun Prabhu</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1183,7 +1183,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Riya Murthy</t>
+          <t>Swathi Nair</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1200,7 +1200,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Vihaan Pai</t>
+          <t>Devansh Nair</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1217,7 +1217,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Shreya Kulkarni</t>
+          <t>Tanya Prabhu</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1234,7 +1234,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Varun Patel</t>
+          <t>Karthik Kumar</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1251,7 +1251,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Pooja Pai</t>
+          <t>Riya Prabhu</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1268,7 +1268,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Devansh Patel</t>
+          <t>Aarav Gowda</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1285,7 +1285,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Swathi Verma</t>
+          <t>Sneha Shetty</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1302,7 +1302,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Vihaan Gowda</t>
+          <t>Aditya Shetty</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1319,7 +1319,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Kavya Iyer</t>
+          <t>Tanya Verma</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1336,7 +1336,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Pranav Desai</t>
+          <t>Yash Naik</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1353,7 +1353,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Pooja Iyer</t>
+          <t>Kritika Bhat</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1370,7 +1370,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Krishna Pai</t>
+          <t>Varun Iyer</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1387,7 +1387,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Shreya Hegde</t>
+          <t>Nisha Bhat</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Siddharth Prabhu</t>
+          <t>Reyansh Nair</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1421,7 +1421,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Kavya Hegde</t>
+          <t>Nisha Gowda</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1438,7 +1438,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Akash Naik</t>
+          <t>Vikram Kulkarni</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1455,7 +1455,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Diya Rao</t>
+          <t>Diya Hegde</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1472,7 +1472,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Aditya Kumar</t>
+          <t>Rahul Prabhu</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1489,7 +1489,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Meera Patel</t>
+          <t>Priya Rao</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1506,7 +1506,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Rahul Murthy</t>
+          <t>Ishaan Iyer</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1523,7 +1523,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Aadhya Hegde</t>
+          <t>Sara Rao</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1611,19 +1611,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C2" t="n">
         <v>98</v>
       </c>
       <c r="D2" t="n">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="E2" t="n">
         <v>95</v>
       </c>
       <c r="F2" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
@@ -1633,7 +1633,11 @@
           <t>Research Design</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr"/>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Outstanding grasp of concepts, sets the benchmark for the class.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1642,33 +1646,29 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="C3" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="D3" t="n">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="E3" t="n">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="F3" t="n">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Qualitative Methods</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>Doing very well overall, minor slips in application-based questions.</t>
-        </is>
-      </c>
+          <t>Research Design</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1677,26 +1677,26 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="C4" t="n">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="D4" t="n">
         <v>81</v>
       </c>
       <c r="E4" t="n">
-        <v>71</v>
+        <v>82</v>
       </c>
       <c r="F4" t="n">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Quantitative Methods</t>
+          <t>Qualitative Methods</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -1708,26 +1708,26 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="C5" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="D5" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="E5" t="n">
-        <v>66</v>
+        <v>56</v>
       </c>
       <c r="F5" t="n">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Data Analysis Tools</t>
+          <t>Qualitative Methods</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1739,28 +1739,24 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>60</v>
+        <v>52</v>
       </c>
       <c r="C6" t="n">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="D6" t="n">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="E6" t="n">
-        <v>62</v>
+        <v>52</v>
       </c>
       <c r="F6" t="n">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
       </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>Research Design</t>
-        </is>
-      </c>
+      <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr"/>
     </row>
     <row r="7">
@@ -1770,19 +1766,19 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="C7" t="n">
-        <v>33</v>
+        <v>50</v>
       </c>
       <c r="D7" t="n">
-        <v>31</v>
+        <v>48</v>
       </c>
       <c r="E7" t="n">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="F7" t="n">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
@@ -1792,11 +1788,7 @@
           <t>Quantitative Methods</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>Below expectations — recommend extra classes after school.</t>
-        </is>
-      </c>
+      <c r="I7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1808,21 +1800,25 @@
         <v>26</v>
       </c>
       <c r="C8" t="n">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="D8" t="n">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="E8" t="n">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="F8" t="n">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
       </c>
-      <c r="H8" t="inlineStr"/>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Research Design</t>
+        </is>
+      </c>
       <c r="I8" t="inlineStr"/>
     </row>
     <row r="9">
@@ -1832,28 +1828,24 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>37</v>
+        <v>28</v>
       </c>
       <c r="C9" t="n">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="D9" t="n">
-        <v>43</v>
+        <v>31</v>
       </c>
       <c r="E9" t="n">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="F9" t="n">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
       </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>Data Analysis Tools</t>
-        </is>
-      </c>
+      <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr"/>
     </row>
     <row r="10">
@@ -1863,19 +1855,19 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="C10" t="n">
-        <v>70</v>
+        <v>81</v>
       </c>
       <c r="D10" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E10" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="F10" t="n">
-        <v>72</v>
+        <v>80</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
@@ -1890,29 +1882,29 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>69</v>
+        <v>56</v>
       </c>
       <c r="C11" t="n">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="D11" t="n">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="E11" t="n">
-        <v>69</v>
+        <v>61</v>
       </c>
       <c r="F11" t="n">
-        <v>69</v>
+        <v>58</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
       </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>Quantitative Methods</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>Inconsistent results — strong in some tests, weak in others.</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1921,25 +1913,33 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C12" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D12" t="n">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="E12" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="F12" t="n">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
       </c>
-      <c r="H12" t="inlineStr"/>
-      <c r="I12" t="inlineStr"/>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Data Analysis Tools</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>Steady but needs more consistency across topics.</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1948,26 +1948,26 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="C13" t="n">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="D13" t="n">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="E13" t="n">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="F13" t="n">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Data Analysis Tools</t>
+          <t>Quantitative Methods</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1979,19 +1979,19 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="C14" t="n">
+        <v>89</v>
+      </c>
+      <c r="D14" t="n">
+        <v>90</v>
+      </c>
+      <c r="E14" t="n">
         <v>92</v>
       </c>
-      <c r="D14" t="n">
-        <v>100</v>
-      </c>
-      <c r="E14" t="n">
-        <v>98</v>
-      </c>
       <c r="F14" t="n">
-        <v>99</v>
+        <v>94</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
@@ -2001,11 +2001,7 @@
           <t>Quantitative Methods</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>Consistently excellent — ready for tougher challenges.</t>
-        </is>
-      </c>
+      <c r="I14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -2014,29 +2010,33 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="C15" t="n">
-        <v>81</v>
+        <v>69</v>
       </c>
       <c r="D15" t="n">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="E15" t="n">
-        <v>81</v>
+        <v>71</v>
       </c>
       <c r="F15" t="n">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Data Analysis Tools</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>Quantitative Methods</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>Solid understanding, encourage attempting harder problems.</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -2045,24 +2045,28 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="C16" t="n">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="D16" t="n">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="E16" t="n">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="F16" t="n">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
       </c>
-      <c r="H16" t="inlineStr"/>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Quantitative Methods</t>
+        </is>
+      </c>
       <c r="I16" t="inlineStr"/>
     </row>
     <row r="17">
@@ -2072,19 +2076,19 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="C17" t="n">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="D17" t="n">
+        <v>54</v>
+      </c>
+      <c r="E17" t="n">
+        <v>59</v>
+      </c>
+      <c r="F17" t="n">
         <v>61</v>
-      </c>
-      <c r="E17" t="n">
-        <v>63</v>
-      </c>
-      <c r="F17" t="n">
-        <v>65</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
@@ -2103,29 +2107,25 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>76</v>
+        <v>61</v>
       </c>
       <c r="C18" t="n">
-        <v>67</v>
+        <v>58</v>
       </c>
       <c r="D18" t="n">
-        <v>70</v>
+        <v>61</v>
       </c>
       <c r="E18" t="n">
+        <v>64</v>
+      </c>
+      <c r="F18" t="n">
         <v>68</v>
       </c>
-      <c r="F18" t="n">
-        <v>65</v>
-      </c>
       <c r="G18" t="n">
         <v>0</v>
       </c>
       <c r="H18" t="inlineStr"/>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>Steady but needs more consistency across topics.</t>
-        </is>
-      </c>
+      <c r="I18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -2134,24 +2134,28 @@
         </is>
       </c>
       <c r="B19" t="n">
+        <v>36</v>
+      </c>
+      <c r="C19" t="n">
+        <v>46</v>
+      </c>
+      <c r="D19" t="n">
         <v>43</v>
       </c>
-      <c r="C19" t="n">
-        <v>38</v>
-      </c>
-      <c r="D19" t="n">
-        <v>39</v>
-      </c>
       <c r="E19" t="n">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="F19" t="n">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
       </c>
-      <c r="H19" t="inlineStr"/>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Quantitative Methods</t>
+        </is>
+      </c>
       <c r="I19" t="inlineStr"/>
     </row>
     <row r="20">
@@ -2161,31 +2165,27 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="C20" t="n">
+        <v>9</v>
+      </c>
+      <c r="D20" t="n">
         <v>16</v>
       </c>
-      <c r="D20" t="n">
-        <v>17</v>
-      </c>
       <c r="E20" t="n">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="F20" t="n">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
       </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>Quantitative Methods</t>
-        </is>
-      </c>
+      <c r="H20" t="inlineStr"/>
       <c r="I20" t="inlineStr">
         <is>
-          <t>Needs urgent academic support, at risk of failing.</t>
+          <t>Very low scores across the board, please involve parents.</t>
         </is>
       </c>
     </row>
@@ -2196,19 +2196,19 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="C21" t="n">
+        <v>33</v>
+      </c>
+      <c r="D21" t="n">
+        <v>28</v>
+      </c>
+      <c r="E21" t="n">
+        <v>34</v>
+      </c>
+      <c r="F21" t="n">
         <v>38</v>
-      </c>
-      <c r="D21" t="n">
-        <v>44</v>
-      </c>
-      <c r="E21" t="n">
-        <v>40</v>
-      </c>
-      <c r="F21" t="n">
-        <v>36</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
@@ -2223,24 +2223,28 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="C22" t="n">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="D22" t="n">
-        <v>70</v>
+        <v>83</v>
       </c>
       <c r="E22" t="n">
-        <v>75</v>
+        <v>88</v>
       </c>
       <c r="F22" t="n">
-        <v>71</v>
+        <v>86</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
       </c>
-      <c r="H22" t="inlineStr"/>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Data Analysis Tools</t>
+        </is>
+      </c>
       <c r="I22" t="inlineStr"/>
     </row>
     <row r="23">
@@ -2250,24 +2254,28 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="C23" t="n">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="D23" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E23" t="n">
-        <v>32</v>
+        <v>43</v>
       </c>
       <c r="F23" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
       </c>
-      <c r="H23" t="inlineStr"/>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Research Design</t>
+        </is>
+      </c>
       <c r="I23" t="inlineStr"/>
     </row>
     <row r="24">
@@ -2277,33 +2285,25 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="C24" t="n">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="D24" t="n">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="E24" t="n">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="F24" t="n">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
       </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>Qualitative Methods</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>Steady but needs more consistency across topics.</t>
-        </is>
-      </c>
+      <c r="H24" t="inlineStr"/>
+      <c r="I24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2312,29 +2312,33 @@
         </is>
       </c>
       <c r="B25" t="n">
+        <v>81</v>
+      </c>
+      <c r="C25" t="n">
+        <v>78</v>
+      </c>
+      <c r="D25" t="n">
+        <v>78</v>
+      </c>
+      <c r="E25" t="n">
+        <v>82</v>
+      </c>
+      <c r="F25" t="n">
         <v>85</v>
       </c>
-      <c r="C25" t="n">
-        <v>91</v>
-      </c>
-      <c r="D25" t="n">
-        <v>91</v>
-      </c>
-      <c r="E25" t="n">
-        <v>90</v>
-      </c>
-      <c r="F25" t="n">
-        <v>81</v>
-      </c>
       <c r="G25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
           <t>Data Analysis Tools</t>
         </is>
       </c>
-      <c r="I25" t="inlineStr"/>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>Solid understanding, encourage attempting harder problems.</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -2343,26 +2347,26 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>88</v>
+        <v>99</v>
       </c>
       <c r="C26" t="n">
-        <v>88</v>
+        <v>98</v>
       </c>
       <c r="D26" t="n">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="E26" t="n">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="F26" t="n">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Research Design</t>
+          <t>Qualitative Methods</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -2374,28 +2378,24 @@
         </is>
       </c>
       <c r="B27" t="n">
+        <v>82</v>
+      </c>
+      <c r="C27" t="n">
         <v>86</v>
       </c>
-      <c r="C27" t="n">
-        <v>79</v>
-      </c>
       <c r="D27" t="n">
-        <v>78</v>
+        <v>92</v>
       </c>
       <c r="E27" t="n">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="F27" t="n">
-        <v>77</v>
+        <v>92</v>
       </c>
       <c r="G27" t="n">
-        <v>0</v>
-      </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>Data Analysis Tools</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="H27" t="inlineStr"/>
       <c r="I27" t="inlineStr"/>
     </row>
     <row r="28">
@@ -2405,28 +2405,24 @@
         </is>
       </c>
       <c r="B28" t="n">
+        <v>77</v>
+      </c>
+      <c r="C28" t="n">
+        <v>85</v>
+      </c>
+      <c r="D28" t="n">
+        <v>77</v>
+      </c>
+      <c r="E28" t="n">
         <v>78</v>
       </c>
-      <c r="C28" t="n">
-        <v>77</v>
-      </c>
-      <c r="D28" t="n">
-        <v>73</v>
-      </c>
-      <c r="E28" t="n">
-        <v>76</v>
-      </c>
       <c r="F28" t="n">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
       </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>Quantitative Methods</t>
-        </is>
-      </c>
+      <c r="H28" t="inlineStr"/>
       <c r="I28" t="inlineStr"/>
     </row>
     <row r="29">
@@ -2436,24 +2432,28 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>69</v>
+        <v>58</v>
       </c>
       <c r="C29" t="n">
-        <v>67</v>
+        <v>58</v>
       </c>
       <c r="D29" t="n">
-        <v>61</v>
+        <v>54</v>
       </c>
       <c r="E29" t="n">
-        <v>70</v>
+        <v>55</v>
       </c>
       <c r="F29" t="n">
-        <v>67</v>
+        <v>60</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
       </c>
-      <c r="H29" t="inlineStr"/>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Qualitative Methods</t>
+        </is>
+      </c>
       <c r="I29" t="inlineStr"/>
     </row>
     <row r="30">
@@ -2463,16 +2463,16 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="C30" t="n">
-        <v>62</v>
+        <v>70</v>
       </c>
       <c r="D30" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="E30" t="n">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="F30" t="n">
         <v>61</v>
@@ -2482,10 +2482,14 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Research Design</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
+          <t>Quantitative Methods</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>On track, but should aim higher with focused practice.</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -2494,24 +2498,28 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="C31" t="n">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="D31" t="n">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="E31" t="n">
+        <v>46</v>
+      </c>
+      <c r="F31" t="n">
         <v>40</v>
       </c>
-      <c r="F31" t="n">
-        <v>31</v>
-      </c>
       <c r="G31" t="n">
         <v>0</v>
       </c>
-      <c r="H31" t="inlineStr"/>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Research Design</t>
+        </is>
+      </c>
       <c r="I31" t="inlineStr"/>
     </row>
   </sheetData>
@@ -2593,28 +2601,24 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>87</v>
+        <v>94</v>
       </c>
       <c r="C2" t="n">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="D2" t="n">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="E2" t="n">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="F2" t="n">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
       </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>Corporate Strategy</t>
-        </is>
-      </c>
+      <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
     </row>
     <row r="3">
@@ -2627,23 +2631,23 @@
         <v>75</v>
       </c>
       <c r="C3" t="n">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="D3" t="n">
+        <v>80</v>
+      </c>
+      <c r="E3" t="n">
         <v>79</v>
       </c>
-      <c r="E3" t="n">
+      <c r="F3" t="n">
         <v>77</v>
       </c>
-      <c r="F3" t="n">
-        <v>82</v>
-      </c>
       <c r="G3" t="n">
         <v>0</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Case Studies</t>
+          <t>Corporate Strategy</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -2655,29 +2659,29 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="C4" t="n">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="D4" t="n">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="E4" t="n">
-        <v>72</v>
+        <v>79</v>
       </c>
       <c r="F4" t="n">
-        <v>75</v>
+        <v>87</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
       </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>Corporate Strategy</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Solid understanding, encourage attempting harder problems.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -2686,33 +2690,25 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="C5" t="n">
-        <v>65</v>
+        <v>57</v>
       </c>
       <c r="D5" t="n">
-        <v>64</v>
+        <v>47</v>
       </c>
       <c r="E5" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="F5" t="n">
-        <v>65</v>
+        <v>54</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
       </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>Strategic Implementation</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>Average performance — revision of basics recommended.</t>
-        </is>
-      </c>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -2721,29 +2717,33 @@
         </is>
       </c>
       <c r="B6" t="n">
+        <v>57</v>
+      </c>
+      <c r="C6" t="n">
+        <v>60</v>
+      </c>
+      <c r="D6" t="n">
         <v>62</v>
       </c>
-      <c r="C6" t="n">
-        <v>57</v>
-      </c>
-      <c r="D6" t="n">
-        <v>67</v>
-      </c>
       <c r="E6" t="n">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="F6" t="n">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Strategic Implementation</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>Corporate Strategy</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>On track, but should aim higher with focused practice.</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -2752,33 +2752,25 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>32</v>
+        <v>44</v>
       </c>
       <c r="C7" t="n">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="D7" t="n">
-        <v>33</v>
+        <v>50</v>
       </c>
       <c r="E7" t="n">
-        <v>33</v>
+        <v>44</v>
       </c>
       <c r="F7" t="n">
-        <v>28</v>
+        <v>50</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
       </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>Strategic Implementation</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>Struggling with fundamentals, needs remedial sessions.</t>
-        </is>
-      </c>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -2787,28 +2779,24 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="C8" t="n">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="D8" t="n">
-        <v>33</v>
+        <v>18</v>
       </c>
       <c r="E8" t="n">
-        <v>34</v>
+        <v>16</v>
       </c>
       <c r="F8" t="n">
-        <v>35</v>
+        <v>19</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
       </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>Strategic Implementation</t>
-        </is>
-      </c>
+      <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr"/>
     </row>
     <row r="9">
@@ -2818,29 +2806,29 @@
         </is>
       </c>
       <c r="B9" t="n">
+        <v>49</v>
+      </c>
+      <c r="C9" t="n">
+        <v>51</v>
+      </c>
+      <c r="D9" t="n">
+        <v>52</v>
+      </c>
+      <c r="E9" t="n">
+        <v>57</v>
+      </c>
+      <c r="F9" t="n">
         <v>47</v>
       </c>
-      <c r="C9" t="n">
-        <v>57</v>
-      </c>
-      <c r="D9" t="n">
-        <v>49</v>
-      </c>
-      <c r="E9" t="n">
-        <v>55</v>
-      </c>
-      <c r="F9" t="n">
-        <v>53</v>
-      </c>
       <c r="G9" t="n">
         <v>0</v>
       </c>
-      <c r="H9" t="inlineStr"/>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>Visible improvement — the extra effort is showing results.</t>
-        </is>
-      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Corporate Strategy</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -2849,19 +2837,19 @@
         </is>
       </c>
       <c r="B10" t="n">
+        <v>57</v>
+      </c>
+      <c r="C10" t="n">
         <v>63</v>
       </c>
-      <c r="C10" t="n">
-        <v>66</v>
-      </c>
       <c r="D10" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E10" t="n">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="F10" t="n">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
@@ -2880,26 +2868,26 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C11" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="D11" t="n">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="E11" t="n">
         <v>77</v>
       </c>
       <c r="F11" t="n">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Strategic Implementation</t>
+          <t>Case Studies</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -2911,28 +2899,24 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>54</v>
+        <v>67</v>
       </c>
       <c r="C12" t="n">
-        <v>55</v>
+        <v>66</v>
       </c>
       <c r="D12" t="n">
-        <v>53</v>
+        <v>65</v>
       </c>
       <c r="E12" t="n">
         <v>60</v>
       </c>
       <c r="F12" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
       </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>Case Studies</t>
-        </is>
-      </c>
+      <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr"/>
     </row>
     <row r="13">
@@ -2942,28 +2926,24 @@
         </is>
       </c>
       <c r="B13" t="n">
+        <v>88</v>
+      </c>
+      <c r="C13" t="n">
+        <v>89</v>
+      </c>
+      <c r="D13" t="n">
+        <v>88</v>
+      </c>
+      <c r="E13" t="n">
         <v>90</v>
       </c>
-      <c r="C13" t="n">
-        <v>87</v>
-      </c>
-      <c r="D13" t="n">
-        <v>84</v>
-      </c>
-      <c r="E13" t="n">
+      <c r="F13" t="n">
         <v>85</v>
       </c>
-      <c r="F13" t="n">
-        <v>90</v>
-      </c>
       <c r="G13" t="n">
         <v>0</v>
       </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>Competitive Strategy</t>
-        </is>
-      </c>
+      <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr"/>
     </row>
     <row r="14">
@@ -2973,29 +2953,29 @@
         </is>
       </c>
       <c r="B14" t="n">
+        <v>95</v>
+      </c>
+      <c r="C14" t="n">
         <v>100</v>
       </c>
-      <c r="C14" t="n">
-        <v>93</v>
-      </c>
       <c r="D14" t="n">
+        <v>96</v>
+      </c>
+      <c r="E14" t="n">
         <v>100</v>
       </c>
-      <c r="E14" t="n">
-        <v>97</v>
-      </c>
       <c r="F14" t="n">
-        <v>99</v>
+        <v>94</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
       </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>Corporate Strategy</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>Exceptional performance, keep up this standard.</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -3004,19 +2984,19 @@
         </is>
       </c>
       <c r="B15" t="n">
+        <v>73</v>
+      </c>
+      <c r="C15" t="n">
+        <v>74</v>
+      </c>
+      <c r="D15" t="n">
+        <v>72</v>
+      </c>
+      <c r="E15" t="n">
+        <v>75</v>
+      </c>
+      <c r="F15" t="n">
         <v>81</v>
-      </c>
-      <c r="C15" t="n">
-        <v>90</v>
-      </c>
-      <c r="D15" t="n">
-        <v>87</v>
-      </c>
-      <c r="E15" t="n">
-        <v>85</v>
-      </c>
-      <c r="F15" t="n">
-        <v>92</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
@@ -3031,24 +3011,28 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="C16" t="n">
         <v>83</v>
       </c>
       <c r="D16" t="n">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="E16" t="n">
+        <v>78</v>
+      </c>
+      <c r="F16" t="n">
         <v>83</v>
       </c>
-      <c r="F16" t="n">
-        <v>84</v>
-      </c>
       <c r="G16" t="n">
         <v>0</v>
       </c>
-      <c r="H16" t="inlineStr"/>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Case Studies</t>
+        </is>
+      </c>
       <c r="I16" t="inlineStr"/>
     </row>
     <row r="17">
@@ -3058,28 +3042,24 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>67</v>
+        <v>58</v>
       </c>
       <c r="C17" t="n">
-        <v>63</v>
+        <v>56</v>
       </c>
       <c r="D17" t="n">
-        <v>62</v>
+        <v>52</v>
       </c>
       <c r="E17" t="n">
         <v>61</v>
       </c>
       <c r="F17" t="n">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
       </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>Case Studies</t>
-        </is>
-      </c>
+      <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr"/>
     </row>
     <row r="18">
@@ -3089,26 +3069,26 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>69</v>
+        <v>54</v>
       </c>
       <c r="C18" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D18" t="n">
-        <v>69</v>
+        <v>56</v>
       </c>
       <c r="E18" t="n">
-        <v>67</v>
+        <v>58</v>
       </c>
       <c r="F18" t="n">
-        <v>70</v>
+        <v>58</v>
       </c>
       <c r="G18" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Corporate Strategy</t>
+          <t>Strategic Implementation</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -3120,29 +3100,29 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="C19" t="n">
-        <v>27</v>
+        <v>43</v>
       </c>
       <c r="D19" t="n">
-        <v>33</v>
+        <v>44</v>
       </c>
       <c r="E19" t="n">
-        <v>33</v>
+        <v>49</v>
       </c>
       <c r="F19" t="n">
-        <v>33</v>
+        <v>44</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
       </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>Strategic Implementation</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>Below expectations — recommend extra classes after school.</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -3151,26 +3131,26 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="C20" t="n">
-        <v>31</v>
+        <v>16</v>
       </c>
       <c r="D20" t="n">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="E20" t="n">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="F20" t="n">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Corporate Strategy</t>
+          <t>Strategic Implementation</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -3182,25 +3162,29 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>47</v>
+        <v>55</v>
       </c>
       <c r="C21" t="n">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="D21" t="n">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="E21" t="n">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="F21" t="n">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
       </c>
       <c r="H21" t="inlineStr"/>
-      <c r="I21" t="inlineStr"/>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>Encouraging progress, on the right track now.</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -3209,26 +3193,26 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="C22" t="n">
-        <v>60</v>
+        <v>73</v>
       </c>
       <c r="D22" t="n">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="E22" t="n">
-        <v>59</v>
+        <v>69</v>
       </c>
       <c r="F22" t="n">
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Corporate Strategy</t>
+          <t>Case Studies</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3240,28 +3224,24 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>74</v>
+        <v>57</v>
       </c>
       <c r="C23" t="n">
-        <v>75</v>
+        <v>48</v>
       </c>
       <c r="D23" t="n">
-        <v>75</v>
+        <v>47</v>
       </c>
       <c r="E23" t="n">
-        <v>74</v>
+        <v>56</v>
       </c>
       <c r="F23" t="n">
-        <v>78</v>
+        <v>47</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
       </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>Case Studies</t>
-        </is>
-      </c>
+      <c r="H23" t="inlineStr"/>
       <c r="I23" t="inlineStr"/>
     </row>
     <row r="24">
@@ -3271,26 +3251,26 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C24" t="n">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="D24" t="n">
-        <v>73</v>
+        <v>66</v>
       </c>
       <c r="E24" t="n">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="F24" t="n">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Corporate Strategy</t>
+          <t>Case Studies</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3302,25 +3282,33 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="C25" t="n">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="D25" t="n">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="E25" t="n">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="F25" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
       </c>
-      <c r="H25" t="inlineStr"/>
-      <c r="I25" t="inlineStr"/>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Strategic Implementation</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>Solid understanding, encourage attempting harder problems.</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -3329,28 +3317,24 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="C26" t="n">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="D26" t="n">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="E26" t="n">
-        <v>97</v>
+        <v>87</v>
       </c>
       <c r="F26" t="n">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
       </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>Competitive Strategy</t>
-        </is>
-      </c>
+      <c r="H26" t="inlineStr"/>
       <c r="I26" t="inlineStr"/>
     </row>
     <row r="27">
@@ -3360,7 +3344,7 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="C27" t="n">
         <v>84</v>
@@ -3369,20 +3353,24 @@
         <v>83</v>
       </c>
       <c r="E27" t="n">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="F27" t="n">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Competitive Strategy</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
+          <t>Case Studies</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>Strong performer, small gains possible with more practice.</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -3391,16 +3379,16 @@
         </is>
       </c>
       <c r="B28" t="n">
+        <v>73</v>
+      </c>
+      <c r="C28" t="n">
+        <v>78</v>
+      </c>
+      <c r="D28" t="n">
+        <v>83</v>
+      </c>
+      <c r="E28" t="n">
         <v>75</v>
-      </c>
-      <c r="C28" t="n">
-        <v>72</v>
-      </c>
-      <c r="D28" t="n">
-        <v>75</v>
-      </c>
-      <c r="E28" t="n">
-        <v>71</v>
       </c>
       <c r="F28" t="n">
         <v>76</v>
@@ -3410,14 +3398,10 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Competitive Strategy</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>Solid understanding, encourage attempting harder problems.</t>
-        </is>
-      </c>
+          <t>Corporate Strategy</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -3429,16 +3413,16 @@
         <v>66</v>
       </c>
       <c r="C29" t="n">
+        <v>56</v>
+      </c>
+      <c r="D29" t="n">
         <v>61</v>
       </c>
-      <c r="D29" t="n">
-        <v>62</v>
-      </c>
       <c r="E29" t="n">
-        <v>64</v>
+        <v>56</v>
       </c>
       <c r="F29" t="n">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
@@ -3453,24 +3437,28 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="C30" t="n">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="D30" t="n">
-        <v>54</v>
+        <v>61</v>
       </c>
       <c r="E30" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F30" t="n">
-        <v>55</v>
+        <v>64</v>
       </c>
       <c r="G30" t="n">
-        <v>0</v>
-      </c>
-      <c r="H30" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Strategic Implementation</t>
+        </is>
+      </c>
       <c r="I30" t="inlineStr"/>
     </row>
     <row r="31">
@@ -3480,28 +3468,24 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="C31" t="n">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="D31" t="n">
         <v>39</v>
       </c>
       <c r="E31" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F31" t="n">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
       </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>Case Studies</t>
-        </is>
-      </c>
+      <c r="H31" t="inlineStr"/>
       <c r="I31" t="inlineStr"/>
     </row>
   </sheetData>
@@ -3583,26 +3567,26 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>84</v>
+        <v>96</v>
       </c>
       <c r="C2" t="n">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="D2" t="n">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="E2" t="n">
-        <v>90</v>
+        <v>97</v>
       </c>
       <c r="F2" t="n">
-        <v>88</v>
+        <v>96</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Data Visualization</t>
+          <t>Descriptive Analytics</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -3614,33 +3598,25 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="C3" t="n">
+        <v>80</v>
+      </c>
+      <c r="D3" t="n">
+        <v>83</v>
+      </c>
+      <c r="E3" t="n">
         <v>82</v>
       </c>
-      <c r="D3" t="n">
-        <v>78</v>
-      </c>
-      <c r="E3" t="n">
-        <v>86</v>
-      </c>
       <c r="F3" t="n">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
       </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>Descriptive Analytics</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>Doing very well overall, minor slips in application-based questions.</t>
-        </is>
-      </c>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -3649,28 +3625,24 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="C4" t="n">
+        <v>86</v>
+      </c>
+      <c r="D4" t="n">
         <v>87</v>
       </c>
-      <c r="D4" t="n">
-        <v>86</v>
-      </c>
       <c r="E4" t="n">
-        <v>88</v>
+        <v>81</v>
       </c>
       <c r="F4" t="n">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="G4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>Business Intelligence Tools</t>
-        </is>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr"/>
     </row>
     <row r="5">
@@ -3680,28 +3652,24 @@
         </is>
       </c>
       <c r="B5" t="n">
+        <v>49</v>
+      </c>
+      <c r="C5" t="n">
         <v>59</v>
       </c>
-      <c r="C5" t="n">
+      <c r="D5" t="n">
+        <v>50</v>
+      </c>
+      <c r="E5" t="n">
+        <v>49</v>
+      </c>
+      <c r="F5" t="n">
         <v>54</v>
       </c>
-      <c r="D5" t="n">
-        <v>59</v>
-      </c>
-      <c r="E5" t="n">
-        <v>61</v>
-      </c>
-      <c r="F5" t="n">
-        <v>51</v>
-      </c>
       <c r="G5" t="n">
         <v>0</v>
       </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>Predictive Modelling</t>
-        </is>
-      </c>
+      <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr">
         <is>
           <t>Steady but needs more consistency across topics.</t>
@@ -3715,19 +3683,19 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C6" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D6" t="n">
-        <v>60</v>
+        <v>51</v>
       </c>
       <c r="E6" t="n">
-        <v>64</v>
+        <v>56</v>
       </c>
       <c r="F6" t="n">
-        <v>62</v>
+        <v>51</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
@@ -3746,29 +3714,29 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>33</v>
+        <v>49</v>
       </c>
       <c r="C7" t="n">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="D7" t="n">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="E7" t="n">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="F7" t="n">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
       </c>
-      <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>Finding it difficult to keep pace, needs individual attention.</t>
-        </is>
-      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Data Visualization</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -3777,29 +3745,33 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="C8" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="D8" t="n">
+        <v>29</v>
+      </c>
+      <c r="E8" t="n">
+        <v>23</v>
+      </c>
+      <c r="F8" t="n">
         <v>27</v>
       </c>
-      <c r="E8" t="n">
-        <v>24</v>
-      </c>
-      <c r="F8" t="n">
-        <v>35</v>
-      </c>
       <c r="G8" t="n">
         <v>0</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Descriptive Analytics</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>Predictive Modelling</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Very low scores across the board, please involve parents.</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -3808,26 +3780,26 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>60</v>
+        <v>73</v>
       </c>
       <c r="C9" t="n">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D9" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="E9" t="n">
-        <v>64</v>
+        <v>75</v>
       </c>
       <c r="F9" t="n">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Predictive Modelling</t>
+          <t>Data Visualization</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -3839,26 +3811,26 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="C10" t="n">
-        <v>50</v>
+        <v>41</v>
       </c>
       <c r="D10" t="n">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="E10" t="n">
-        <v>50</v>
+        <v>34</v>
       </c>
       <c r="F10" t="n">
-        <v>47</v>
+        <v>37</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Descriptive Analytics</t>
+          <t>Business Intelligence Tools</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -3870,28 +3842,24 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>33</v>
+        <v>72</v>
       </c>
       <c r="C11" t="n">
-        <v>33</v>
+        <v>69</v>
       </c>
       <c r="D11" t="n">
-        <v>35</v>
+        <v>70</v>
       </c>
       <c r="E11" t="n">
-        <v>36</v>
+        <v>74</v>
       </c>
       <c r="F11" t="n">
-        <v>29</v>
+        <v>69</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
       </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>Data Visualization</t>
-        </is>
-      </c>
+      <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr"/>
     </row>
     <row r="12">
@@ -3901,29 +3869,33 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>55</v>
+        <v>64</v>
       </c>
       <c r="C12" t="n">
+        <v>64</v>
+      </c>
+      <c r="D12" t="n">
         <v>60</v>
       </c>
-      <c r="D12" t="n">
-        <v>53</v>
-      </c>
       <c r="E12" t="n">
-        <v>56</v>
+        <v>64</v>
       </c>
       <c r="F12" t="n">
-        <v>53</v>
+        <v>66</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Business Intelligence Tools</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>Data Visualization</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>On track, but should aim higher with focused practice.</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -3932,19 +3904,19 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="C13" t="n">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="D13" t="n">
         <v>83</v>
       </c>
       <c r="E13" t="n">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="F13" t="n">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
@@ -3954,11 +3926,7 @@
           <t>Descriptive Analytics</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>Solid understanding, encourage attempting harder problems.</t>
-        </is>
-      </c>
+      <c r="I13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -3967,33 +3935,29 @@
         </is>
       </c>
       <c r="B14" t="n">
+        <v>95</v>
+      </c>
+      <c r="C14" t="n">
+        <v>94</v>
+      </c>
+      <c r="D14" t="n">
         <v>100</v>
       </c>
-      <c r="C14" t="n">
-        <v>99</v>
-      </c>
-      <c r="D14" t="n">
-        <v>99</v>
-      </c>
       <c r="E14" t="n">
-        <v>100</v>
+        <v>93</v>
       </c>
       <c r="F14" t="n">
-        <v>100</v>
+        <v>92</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Descriptive Analytics</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>Consistently excellent — ready for tougher challenges.</t>
-        </is>
-      </c>
+          <t>Data Visualization</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -4002,31 +3966,31 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="C15" t="n">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="E15" t="n">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="F15" t="n">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Business Intelligence Tools</t>
+          <t>Data Visualization</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>Doing very well overall, minor slips in application-based questions.</t>
+          <t>Solid understanding, encourage attempting harder problems.</t>
         </is>
       </c>
     </row>
@@ -4037,19 +4001,19 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="C16" t="n">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="D16" t="n">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="E16" t="n">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="F16" t="n">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
@@ -4068,26 +4032,26 @@
         </is>
       </c>
       <c r="B17" t="n">
+        <v>57</v>
+      </c>
+      <c r="C17" t="n">
+        <v>62</v>
+      </c>
+      <c r="D17" t="n">
+        <v>56</v>
+      </c>
+      <c r="E17" t="n">
         <v>55</v>
       </c>
-      <c r="C17" t="n">
-        <v>64</v>
-      </c>
-      <c r="D17" t="n">
-        <v>64</v>
-      </c>
-      <c r="E17" t="n">
-        <v>56</v>
-      </c>
       <c r="F17" t="n">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Data Visualization</t>
+          <t>Business Intelligence Tools</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -4099,26 +4063,26 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>71</v>
+        <v>59</v>
       </c>
       <c r="C18" t="n">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="D18" t="n">
+        <v>62</v>
+      </c>
+      <c r="E18" t="n">
+        <v>63</v>
+      </c>
+      <c r="F18" t="n">
         <v>68</v>
       </c>
-      <c r="E18" t="n">
-        <v>71</v>
-      </c>
-      <c r="F18" t="n">
-        <v>66</v>
-      </c>
       <c r="G18" t="n">
         <v>0</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Descriptive Analytics</t>
+          <t>Business Intelligence Tools</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -4130,28 +4094,24 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>26</v>
+        <v>45</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>48</v>
       </c>
       <c r="D19" t="n">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="E19" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="F19" t="n">
-        <v>34</v>
+        <v>44</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
       </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>Data Visualization</t>
-        </is>
-      </c>
+      <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr"/>
     </row>
     <row r="20">
@@ -4161,24 +4121,28 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="C20" t="n">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="D20" t="n">
-        <v>22</v>
+        <v>5</v>
       </c>
       <c r="E20" t="n">
-        <v>27</v>
+        <v>7</v>
       </c>
       <c r="F20" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
       </c>
-      <c r="H20" t="inlineStr"/>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Data Visualization</t>
+        </is>
+      </c>
       <c r="I20" t="inlineStr"/>
     </row>
     <row r="21">
@@ -4191,26 +4155,22 @@
         <v>67</v>
       </c>
       <c r="C21" t="n">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="D21" t="n">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="E21" t="n">
-        <v>67</v>
+        <v>75</v>
       </c>
       <c r="F21" t="n">
-        <v>63</v>
+        <v>75</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
       </c>
       <c r="H21" t="inlineStr"/>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>Visible improvement — the extra effort is showing results.</t>
-        </is>
-      </c>
+      <c r="I21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -4222,16 +4182,16 @@
         <v>41</v>
       </c>
       <c r="C22" t="n">
+        <v>46</v>
+      </c>
+      <c r="D22" t="n">
+        <v>47</v>
+      </c>
+      <c r="E22" t="n">
+        <v>48</v>
+      </c>
+      <c r="F22" t="n">
         <v>41</v>
-      </c>
-      <c r="D22" t="n">
-        <v>51</v>
-      </c>
-      <c r="E22" t="n">
-        <v>41</v>
-      </c>
-      <c r="F22" t="n">
-        <v>51</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
@@ -4250,19 +4210,19 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>74</v>
+        <v>48</v>
       </c>
       <c r="C23" t="n">
-        <v>73</v>
+        <v>52</v>
       </c>
       <c r="D23" t="n">
-        <v>65</v>
+        <v>47</v>
       </c>
       <c r="E23" t="n">
-        <v>70</v>
+        <v>52</v>
       </c>
       <c r="F23" t="n">
-        <v>65</v>
+        <v>54</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
@@ -4277,16 +4237,16 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>73</v>
+        <v>66</v>
       </c>
       <c r="C24" t="n">
         <v>69</v>
       </c>
       <c r="D24" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E24" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="F24" t="n">
         <v>70</v>
@@ -4299,7 +4259,11 @@
           <t>Business Intelligence Tools</t>
         </is>
       </c>
-      <c r="I24" t="inlineStr"/>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>Average performance — revision of basics recommended.</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -4308,28 +4272,24 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="C25" t="n">
         <v>87</v>
       </c>
       <c r="D25" t="n">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="E25" t="n">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="F25" t="n">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
       </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>Business Intelligence Tools</t>
-        </is>
-      </c>
+      <c r="H25" t="inlineStr"/>
       <c r="I25" t="inlineStr"/>
     </row>
     <row r="26">
@@ -4339,26 +4299,26 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="C26" t="n">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="D26" t="n">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="E26" t="n">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="F26" t="n">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Business Intelligence Tools</t>
+          <t>Predictive Modelling</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -4370,26 +4330,26 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="C27" t="n">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D27" t="n">
-        <v>81</v>
+        <v>88</v>
       </c>
       <c r="E27" t="n">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="F27" t="n">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Data Visualization</t>
+          <t>Business Intelligence Tools</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -4401,28 +4361,24 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="C28" t="n">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="D28" t="n">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="E28" t="n">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="F28" t="n">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
       </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>Business Intelligence Tools</t>
-        </is>
-      </c>
+      <c r="H28" t="inlineStr"/>
       <c r="I28" t="inlineStr"/>
     </row>
     <row r="29">
@@ -4432,29 +4388,29 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>71</v>
+        <v>52</v>
       </c>
       <c r="C29" t="n">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="D29" t="n">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="E29" t="n">
-        <v>70</v>
+        <v>54</v>
       </c>
       <c r="F29" t="n">
-        <v>70</v>
+        <v>52</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
       </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>Predictive Modelling</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
+      <c r="H29" t="inlineStr"/>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>On track, but should aim higher with focused practice.</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -4463,33 +4419,25 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="C30" t="n">
         <v>55</v>
       </c>
       <c r="D30" t="n">
-        <v>55</v>
+        <v>61</v>
       </c>
       <c r="E30" t="n">
         <v>59</v>
       </c>
       <c r="F30" t="n">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
       </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>Predictive Modelling</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>Steady but needs more consistency across topics.</t>
-        </is>
-      </c>
+      <c r="H30" t="inlineStr"/>
+      <c r="I30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -4498,29 +4446,33 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="C31" t="n">
-        <v>30</v>
+        <v>44</v>
       </c>
       <c r="D31" t="n">
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="E31" t="n">
-        <v>33</v>
+        <v>51</v>
       </c>
       <c r="F31" t="n">
-        <v>34</v>
+        <v>49</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Business Intelligence Tools</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
+          <t>Predictive Modelling</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>Below expectations — recommend extra classes after school.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4601,28 +4553,24 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="C2" t="n">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="D2" t="n">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="E2" t="n">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="F2" t="n">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
       </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>International Trade</t>
-        </is>
-      </c>
+      <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr">
         <is>
           <t>Consistently excellent — ready for tougher challenges.</t>
@@ -4639,16 +4587,16 @@
         <v>82</v>
       </c>
       <c r="C3" t="n">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="D3" t="n">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="E3" t="n">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="F3" t="n">
-        <v>74</v>
+        <v>84</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
@@ -4656,7 +4604,7 @@
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Solid understanding, encourage attempting harder problems.</t>
+          <t>Strong performer, small gains possible with more practice.</t>
         </is>
       </c>
     </row>
@@ -4667,27 +4615,31 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="C4" t="n">
+        <v>88</v>
+      </c>
+      <c r="D4" t="n">
+        <v>93</v>
+      </c>
+      <c r="E4" t="n">
         <v>87</v>
       </c>
-      <c r="D4" t="n">
-        <v>88</v>
-      </c>
-      <c r="E4" t="n">
-        <v>90</v>
-      </c>
       <c r="F4" t="n">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
       </c>
-      <c r="H4" t="inlineStr"/>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Global Supply Chains</t>
+        </is>
+      </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Strong performer, small gains possible with more practice.</t>
+          <t>Doing very well overall, minor slips in application-based questions.</t>
         </is>
       </c>
     </row>
@@ -4704,18 +4656,22 @@
         <v>61</v>
       </c>
       <c r="D5" t="n">
-        <v>63</v>
+        <v>56</v>
       </c>
       <c r="E5" t="n">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="F5" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
       </c>
-      <c r="H5" t="inlineStr"/>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>International Trade</t>
+        </is>
+      </c>
       <c r="I5" t="inlineStr">
         <is>
           <t>Steady but needs more consistency across topics.</t>
@@ -4729,24 +4685,28 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="C6" t="n">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="D6" t="n">
+        <v>59</v>
+      </c>
+      <c r="E6" t="n">
+        <v>62</v>
+      </c>
+      <c r="F6" t="n">
         <v>61</v>
       </c>
-      <c r="E6" t="n">
-        <v>56</v>
-      </c>
-      <c r="F6" t="n">
-        <v>60</v>
-      </c>
       <c r="G6" t="n">
         <v>0</v>
       </c>
-      <c r="H6" t="inlineStr"/>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>International Trade</t>
+        </is>
+      </c>
       <c r="I6" t="inlineStr">
         <is>
           <t>Average performance — revision of basics recommended.</t>
@@ -4760,19 +4720,19 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>32</v>
+        <v>43</v>
       </c>
       <c r="C7" t="n">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="D7" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E7" t="n">
-        <v>32</v>
+        <v>44</v>
       </c>
       <c r="F7" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
@@ -4784,7 +4744,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Struggling with fundamentals, needs remedial sessions.</t>
+          <t>Below expectations — recommend extra classes after school.</t>
         </is>
       </c>
     </row>
@@ -4795,27 +4755,31 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="C8" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="D8" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E8" t="n">
-        <v>35</v>
+        <v>22</v>
       </c>
       <c r="F8" t="n">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
       </c>
-      <c r="H8" t="inlineStr"/>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Emerging Markets</t>
+        </is>
+      </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Very low scores across the board, please involve parents.</t>
+          <t>Needs urgent academic support, at risk of failing.</t>
         </is>
       </c>
     </row>
@@ -4826,19 +4790,19 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="C9" t="n">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="D9" t="n">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="E9" t="n">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="F9" t="n">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
@@ -4846,7 +4810,7 @@
       <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Visible improvement — the extra effort is showing results.</t>
+          <t>Great turnaround this term, keep the momentum going!</t>
         </is>
       </c>
     </row>
@@ -4857,31 +4821,31 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="C10" t="n">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="D10" t="n">
-        <v>27</v>
+        <v>9</v>
       </c>
       <c r="E10" t="n">
-        <v>35</v>
+        <v>9</v>
       </c>
       <c r="F10" t="n">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Global Supply Chains</t>
+          <t>International Trade</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Needs attention — performance has slipped recently.</t>
+          <t>Was doing well earlier, something seems to be affecting focus now.</t>
         </is>
       </c>
     </row>
@@ -4892,27 +4856,31 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>39</v>
+        <v>49</v>
       </c>
       <c r="C11" t="n">
-        <v>29</v>
+        <v>60</v>
       </c>
       <c r="D11" t="n">
-        <v>40</v>
+        <v>56</v>
       </c>
       <c r="E11" t="n">
-        <v>32</v>
+        <v>59</v>
       </c>
       <c r="F11" t="n">
-        <v>35</v>
+        <v>51</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
       </c>
-      <c r="H11" t="inlineStr"/>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Emerging Markets</t>
+        </is>
+      </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Inconsistent results — strong in some tests, weak in others.</t>
+          <t>Unpredictable performance, may help to identify what's different on good days.</t>
         </is>
       </c>
     </row>
@@ -4923,19 +4891,19 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="C12" t="n">
-        <v>61</v>
+        <v>54</v>
       </c>
       <c r="D12" t="n">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="E12" t="n">
-        <v>66</v>
+        <v>57</v>
       </c>
       <c r="F12" t="n">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
@@ -4958,19 +4926,19 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="C13" t="n">
-        <v>91</v>
+        <v>76</v>
       </c>
       <c r="D13" t="n">
-        <v>95</v>
+        <v>82</v>
       </c>
       <c r="E13" t="n">
-        <v>94</v>
+        <v>87</v>
       </c>
       <c r="F13" t="n">
-        <v>94</v>
+        <v>76</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
@@ -4982,7 +4950,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Strong performer, small gains possible with more practice.</t>
+          <t>Doing very well overall, minor slips in application-based questions.</t>
         </is>
       </c>
     </row>
@@ -4993,19 +4961,19 @@
         </is>
       </c>
       <c r="B14" t="n">
+        <v>100</v>
+      </c>
+      <c r="C14" t="n">
+        <v>98</v>
+      </c>
+      <c r="D14" t="n">
+        <v>100</v>
+      </c>
+      <c r="E14" t="n">
         <v>95</v>
       </c>
-      <c r="C14" t="n">
+      <c r="F14" t="n">
         <v>97</v>
-      </c>
-      <c r="D14" t="n">
-        <v>91</v>
-      </c>
-      <c r="E14" t="n">
-        <v>90</v>
-      </c>
-      <c r="F14" t="n">
-        <v>94</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
@@ -5028,31 +4996,31 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="C15" t="n">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="D15" t="n">
-        <v>85</v>
+        <v>71</v>
       </c>
       <c r="E15" t="n">
-        <v>79</v>
+        <v>70</v>
       </c>
       <c r="F15" t="n">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>International Trade</t>
+          <t>Global Supply Chains</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>Doing very well overall, minor slips in application-based questions.</t>
+          <t>Strong performer, small gains possible with more practice.</t>
         </is>
       </c>
     </row>
@@ -5063,24 +5031,28 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="C16" t="n">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="D16" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E16" t="n">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="F16" t="n">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
       </c>
-      <c r="H16" t="inlineStr"/>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>International Trade</t>
+        </is>
+      </c>
       <c r="I16" t="inlineStr">
         <is>
           <t>Solid understanding, encourage attempting harder problems.</t>
@@ -5094,19 +5066,19 @@
         </is>
       </c>
       <c r="B17" t="n">
+        <v>58</v>
+      </c>
+      <c r="C17" t="n">
         <v>64</v>
       </c>
-      <c r="C17" t="n">
-        <v>63</v>
-      </c>
       <c r="D17" t="n">
-        <v>69</v>
+        <v>57</v>
       </c>
       <c r="E17" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="F17" t="n">
-        <v>71</v>
+        <v>58</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
@@ -5118,7 +5090,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>Average performance — revision of basics recommended.</t>
+          <t>Steady but needs more consistency across topics.</t>
         </is>
       </c>
     </row>
@@ -5129,31 +5101,31 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="C18" t="n">
         <v>67</v>
       </c>
       <c r="D18" t="n">
+        <v>60</v>
+      </c>
+      <c r="E18" t="n">
         <v>63</v>
       </c>
-      <c r="E18" t="n">
-        <v>61</v>
-      </c>
       <c r="F18" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>International Trade</t>
+          <t>Exchange Rate Systems</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Average performance — revision of basics recommended.</t>
+          <t>Steady but needs more consistency across topics.</t>
         </is>
       </c>
     </row>
@@ -5164,19 +5136,19 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="C19" t="n">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="D19" t="n">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="E19" t="n">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="F19" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
@@ -5199,31 +5171,31 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="C20" t="n">
-        <v>27</v>
+        <v>8</v>
       </c>
       <c r="D20" t="n">
-        <v>31</v>
+        <v>6</v>
       </c>
       <c r="E20" t="n">
-        <v>27</v>
+        <v>11</v>
       </c>
       <c r="F20" t="n">
-        <v>28</v>
+        <v>14</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Global Supply Chains</t>
+          <t>Emerging Markets</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>Needs urgent academic support, at risk of failing.</t>
+          <t>Very low scores across the board, please involve parents.</t>
         </is>
       </c>
     </row>
@@ -5234,31 +5206,31 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="C21" t="n">
         <v>85</v>
       </c>
       <c r="D21" t="n">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="E21" t="n">
-        <v>85</v>
+        <v>93</v>
       </c>
       <c r="F21" t="n">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Global Supply Chains</t>
+          <t>Emerging Markets</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>Encouraging progress, on the right track now.</t>
+          <t>Visible improvement — the extra effort is showing results.</t>
         </is>
       </c>
     </row>
@@ -5269,20 +5241,20 @@
         </is>
       </c>
       <c r="B22" t="n">
+        <v>22</v>
+      </c>
+      <c r="C22" t="n">
+        <v>29</v>
+      </c>
+      <c r="D22" t="n">
+        <v>21</v>
+      </c>
+      <c r="E22" t="n">
+        <v>29</v>
+      </c>
+      <c r="F22" t="n">
         <v>25</v>
       </c>
-      <c r="C22" t="n">
-        <v>26</v>
-      </c>
-      <c r="D22" t="n">
-        <v>30</v>
-      </c>
-      <c r="E22" t="n">
-        <v>25</v>
-      </c>
-      <c r="F22" t="n">
-        <v>27</v>
-      </c>
       <c r="G22" t="n">
         <v>0</v>
       </c>
@@ -5293,7 +5265,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>Was doing well earlier, something seems to be affecting focus now.</t>
+          <t>Needs attention — performance has slipped recently.</t>
         </is>
       </c>
     </row>
@@ -5304,31 +5276,31 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="C23" t="n">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="D23" t="n">
-        <v>85</v>
+        <v>72</v>
       </c>
       <c r="E23" t="n">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="F23" t="n">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Emerging Markets</t>
+          <t>Global Supply Chains</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>Ups and downs need to be understood — talk to student directly.</t>
+          <t>Unpredictable performance, may help to identify what's different on good days.</t>
         </is>
       </c>
     </row>
@@ -5342,28 +5314,28 @@
         <v>68</v>
       </c>
       <c r="C24" t="n">
+        <v>63</v>
+      </c>
+      <c r="D24" t="n">
         <v>65</v>
       </c>
-      <c r="D24" t="n">
+      <c r="E24" t="n">
         <v>70</v>
       </c>
-      <c r="E24" t="n">
-        <v>72</v>
-      </c>
       <c r="F24" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Exchange Rate Systems</t>
+          <t>Emerging Markets</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>Steady but needs more consistency across topics.</t>
+          <t>Average performance — revision of basics recommended.</t>
         </is>
       </c>
     </row>
@@ -5374,26 +5346,26 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="C25" t="n">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="D25" t="n">
+        <v>85</v>
+      </c>
+      <c r="E25" t="n">
         <v>79</v>
       </c>
-      <c r="E25" t="n">
-        <v>84</v>
-      </c>
       <c r="F25" t="n">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="G25" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>International Trade</t>
+          <t>Global Supply Chains</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -5409,19 +5381,19 @@
         </is>
       </c>
       <c r="B26" t="n">
+        <v>94</v>
+      </c>
+      <c r="C26" t="n">
+        <v>92</v>
+      </c>
+      <c r="D26" t="n">
         <v>86</v>
       </c>
-      <c r="C26" t="n">
-        <v>88</v>
-      </c>
-      <c r="D26" t="n">
-        <v>88</v>
-      </c>
       <c r="E26" t="n">
+        <v>85</v>
+      </c>
+      <c r="F26" t="n">
         <v>90</v>
-      </c>
-      <c r="F26" t="n">
-        <v>87</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
@@ -5429,7 +5401,7 @@
       <c r="H26" t="inlineStr"/>
       <c r="I26" t="inlineStr">
         <is>
-          <t>Outstanding grasp of concepts, sets the benchmark for the class.</t>
+          <t>Exceptional performance, keep up this standard.</t>
         </is>
       </c>
     </row>
@@ -5440,31 +5412,31 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="C27" t="n">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="D27" t="n">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="E27" t="n">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="F27" t="n">
-        <v>72</v>
+        <v>86</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Exchange Rate Systems</t>
+          <t>Global Supply Chains</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>Strong performer, small gains possible with more practice.</t>
+          <t>Doing very well overall, minor slips in application-based questions.</t>
         </is>
       </c>
     </row>
@@ -5475,27 +5447,31 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="C28" t="n">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="D28" t="n">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="E28" t="n">
         <v>80</v>
       </c>
       <c r="F28" t="n">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
       </c>
-      <c r="H28" t="inlineStr"/>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>International Trade</t>
+        </is>
+      </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>Strong performer, small gains possible with more practice.</t>
+          <t>Doing very well overall, minor slips in application-based questions.</t>
         </is>
       </c>
     </row>
@@ -5506,31 +5482,27 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="C29" t="n">
-        <v>67</v>
+        <v>57</v>
       </c>
       <c r="D29" t="n">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="E29" t="n">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="F29" t="n">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
       </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>Global Supply Chains</t>
-        </is>
-      </c>
+      <c r="H29" t="inlineStr"/>
       <c r="I29" t="inlineStr">
         <is>
-          <t>On track, but should aim higher with focused practice.</t>
+          <t>Average performance — revision of basics recommended.</t>
         </is>
       </c>
     </row>
@@ -5541,19 +5513,19 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>54</v>
+        <v>64</v>
       </c>
       <c r="C30" t="n">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="D30" t="n">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="E30" t="n">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="F30" t="n">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
@@ -5572,28 +5544,24 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="C31" t="n">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="D31" t="n">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="E31" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F31" t="n">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
       </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>Emerging Markets</t>
-        </is>
-      </c>
+      <c r="H31" t="inlineStr"/>
       <c r="I31" t="inlineStr">
         <is>
           <t>Struggling with fundamentals, needs remedial sessions.</t>

--- a/samples/Sample_3_For_International_Masters_College.xlsx
+++ b/samples/Sample_3_For_International_Masters_College.xlsx
@@ -9,10 +9,10 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SETUP" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="STUDENTS" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Module Assessment 1" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Module Assessment 2" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Module Assessment 3" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Module Assessment 4" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MBA2025-Module Assessment 1" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MBA2025-Module Assessment 2" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MBA2025-Module Assessment 3" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MBA2025-Module Assessment 4" sheetId="6" state="visible" r:id="rId6"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
@@ -525,7 +525,6 @@
           <t>Section</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -633,7 +632,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Module Assessment 1</t>
+          <t>MBA2025-Module Assessment 1</t>
         </is>
       </c>
     </row>
@@ -702,7 +701,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Module Assessment 2</t>
+          <t>MBA2025-Module Assessment 2</t>
         </is>
       </c>
     </row>
@@ -771,7 +770,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Module Assessment 3</t>
+          <t>MBA2025-Module Assessment 3</t>
         </is>
       </c>
     </row>
@@ -840,7 +839,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Module Assessment 4</t>
+          <t>MBA2025-Module Assessment 4</t>
         </is>
       </c>
     </row>
@@ -1668,7 +1667,6 @@
           <t>Research Design</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1699,7 +1697,6 @@
           <t>Qualitative Methods</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1730,7 +1727,6 @@
           <t>Qualitative Methods</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1756,8 +1752,6 @@
       <c r="G6" t="n">
         <v>0</v>
       </c>
-      <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1788,7 +1782,6 @@
           <t>Quantitative Methods</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1819,7 +1812,6 @@
           <t>Research Design</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1845,8 +1837,6 @@
       <c r="G9" t="n">
         <v>0</v>
       </c>
-      <c r="H9" t="inlineStr"/>
-      <c r="I9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1872,8 +1862,6 @@
       <c r="G10" t="n">
         <v>0</v>
       </c>
-      <c r="H10" t="inlineStr"/>
-      <c r="I10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1899,7 +1887,6 @@
       <c r="G11" t="n">
         <v>0</v>
       </c>
-      <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr">
         <is>
           <t>Inconsistent results — strong in some tests, weak in others.</t>
@@ -1970,7 +1957,6 @@
           <t>Quantitative Methods</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -2001,7 +1987,6 @@
           <t>Quantitative Methods</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -2067,7 +2052,6 @@
           <t>Quantitative Methods</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -2098,7 +2082,6 @@
           <t>Research Design</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -2124,8 +2107,6 @@
       <c r="G18" t="n">
         <v>0</v>
       </c>
-      <c r="H18" t="inlineStr"/>
-      <c r="I18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -2156,7 +2137,6 @@
           <t>Quantitative Methods</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2182,7 +2162,6 @@
       <c r="G20" t="n">
         <v>0</v>
       </c>
-      <c r="H20" t="inlineStr"/>
       <c r="I20" t="inlineStr">
         <is>
           <t>Very low scores across the board, please involve parents.</t>
@@ -2213,8 +2192,6 @@
       <c r="G21" t="n">
         <v>0</v>
       </c>
-      <c r="H21" t="inlineStr"/>
-      <c r="I21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2245,7 +2222,6 @@
           <t>Data Analysis Tools</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2276,7 +2252,6 @@
           <t>Research Design</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2302,8 +2277,6 @@
       <c r="G24" t="n">
         <v>0</v>
       </c>
-      <c r="H24" t="inlineStr"/>
-      <c r="I24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2369,7 +2342,6 @@
           <t>Qualitative Methods</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -2395,8 +2367,6 @@
       <c r="G27" t="n">
         <v>1</v>
       </c>
-      <c r="H27" t="inlineStr"/>
-      <c r="I27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -2422,8 +2392,6 @@
       <c r="G28" t="n">
         <v>0</v>
       </c>
-      <c r="H28" t="inlineStr"/>
-      <c r="I28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -2454,7 +2422,6 @@
           <t>Qualitative Methods</t>
         </is>
       </c>
-      <c r="I29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -2520,7 +2487,6 @@
           <t>Research Design</t>
         </is>
       </c>
-      <c r="I31" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2618,8 +2584,6 @@
       <c r="G2" t="n">
         <v>0</v>
       </c>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -2650,7 +2614,6 @@
           <t>Corporate Strategy</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -2676,7 +2639,6 @@
       <c r="G4" t="n">
         <v>0</v>
       </c>
-      <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr">
         <is>
           <t>Solid understanding, encourage attempting harder problems.</t>
@@ -2707,8 +2669,6 @@
       <c r="G5" t="n">
         <v>0</v>
       </c>
-      <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -2769,8 +2729,6 @@
       <c r="G7" t="n">
         <v>0</v>
       </c>
-      <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -2796,8 +2754,6 @@
       <c r="G8" t="n">
         <v>0</v>
       </c>
-      <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -2828,7 +2784,6 @@
           <t>Corporate Strategy</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -2859,7 +2814,6 @@
           <t>Corporate Strategy</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -2890,7 +2844,6 @@
           <t>Case Studies</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -2916,8 +2869,6 @@
       <c r="G12" t="n">
         <v>0</v>
       </c>
-      <c r="H12" t="inlineStr"/>
-      <c r="I12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -2943,8 +2894,6 @@
       <c r="G13" t="n">
         <v>0</v>
       </c>
-      <c r="H13" t="inlineStr"/>
-      <c r="I13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -2970,7 +2919,6 @@
       <c r="G14" t="n">
         <v>0</v>
       </c>
-      <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr">
         <is>
           <t>Exceptional performance, keep up this standard.</t>
@@ -3001,8 +2949,6 @@
       <c r="G15" t="n">
         <v>0</v>
       </c>
-      <c r="H15" t="inlineStr"/>
-      <c r="I15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -3033,7 +2979,6 @@
           <t>Case Studies</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -3059,8 +3004,6 @@
       <c r="G17" t="n">
         <v>0</v>
       </c>
-      <c r="H17" t="inlineStr"/>
-      <c r="I17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -3091,7 +3034,6 @@
           <t>Strategic Implementation</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -3117,7 +3059,6 @@
       <c r="G19" t="n">
         <v>0</v>
       </c>
-      <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr">
         <is>
           <t>Below expectations — recommend extra classes after school.</t>
@@ -3153,7 +3094,6 @@
           <t>Strategic Implementation</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -3179,7 +3119,6 @@
       <c r="G21" t="n">
         <v>0</v>
       </c>
-      <c r="H21" t="inlineStr"/>
       <c r="I21" t="inlineStr">
         <is>
           <t>Encouraging progress, on the right track now.</t>
@@ -3215,7 +3154,6 @@
           <t>Case Studies</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -3241,8 +3179,6 @@
       <c r="G23" t="n">
         <v>0</v>
       </c>
-      <c r="H23" t="inlineStr"/>
-      <c r="I23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -3273,7 +3209,6 @@
           <t>Case Studies</t>
         </is>
       </c>
-      <c r="I24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -3334,8 +3269,6 @@
       <c r="G26" t="n">
         <v>0</v>
       </c>
-      <c r="H26" t="inlineStr"/>
-      <c r="I26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -3401,7 +3334,6 @@
           <t>Corporate Strategy</t>
         </is>
       </c>
-      <c r="I28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -3427,8 +3359,6 @@
       <c r="G29" t="n">
         <v>0</v>
       </c>
-      <c r="H29" t="inlineStr"/>
-      <c r="I29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -3459,7 +3389,6 @@
           <t>Strategic Implementation</t>
         </is>
       </c>
-      <c r="I30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -3485,8 +3414,6 @@
       <c r="G31" t="n">
         <v>0</v>
       </c>
-      <c r="H31" t="inlineStr"/>
-      <c r="I31" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3589,7 +3516,6 @@
           <t>Descriptive Analytics</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -3615,8 +3541,6 @@
       <c r="G3" t="n">
         <v>0</v>
       </c>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -3642,8 +3566,6 @@
       <c r="G4" t="n">
         <v>2</v>
       </c>
-      <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -3669,7 +3591,6 @@
       <c r="G5" t="n">
         <v>0</v>
       </c>
-      <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr">
         <is>
           <t>Steady but needs more consistency across topics.</t>
@@ -3705,7 +3626,6 @@
           <t>Business Intelligence Tools</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -3736,7 +3656,6 @@
           <t>Data Visualization</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -3802,7 +3721,6 @@
           <t>Data Visualization</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -3833,7 +3751,6 @@
           <t>Business Intelligence Tools</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -3859,8 +3776,6 @@
       <c r="G11" t="n">
         <v>0</v>
       </c>
-      <c r="H11" t="inlineStr"/>
-      <c r="I11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -3926,7 +3841,6 @@
           <t>Descriptive Analytics</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -3957,7 +3871,6 @@
           <t>Data Visualization</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -4023,7 +3936,6 @@
           <t>Descriptive Analytics</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -4054,7 +3966,6 @@
           <t>Business Intelligence Tools</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -4085,7 +3996,6 @@
           <t>Business Intelligence Tools</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -4111,8 +4021,6 @@
       <c r="G19" t="n">
         <v>0</v>
       </c>
-      <c r="H19" t="inlineStr"/>
-      <c r="I19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -4143,7 +4051,6 @@
           <t>Data Visualization</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -4169,8 +4076,6 @@
       <c r="G21" t="n">
         <v>0</v>
       </c>
-      <c r="H21" t="inlineStr"/>
-      <c r="I21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -4201,7 +4106,6 @@
           <t>Data Visualization</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -4227,8 +4131,6 @@
       <c r="G23" t="n">
         <v>0</v>
       </c>
-      <c r="H23" t="inlineStr"/>
-      <c r="I23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -4289,8 +4191,6 @@
       <c r="G25" t="n">
         <v>0</v>
       </c>
-      <c r="H25" t="inlineStr"/>
-      <c r="I25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -4321,7 +4221,6 @@
           <t>Predictive Modelling</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -4352,7 +4251,6 @@
           <t>Business Intelligence Tools</t>
         </is>
       </c>
-      <c r="I27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -4378,8 +4276,6 @@
       <c r="G28" t="n">
         <v>0</v>
       </c>
-      <c r="H28" t="inlineStr"/>
-      <c r="I28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -4405,7 +4301,6 @@
       <c r="G29" t="n">
         <v>0</v>
       </c>
-      <c r="H29" t="inlineStr"/>
       <c r="I29" t="inlineStr">
         <is>
           <t>On track, but should aim higher with focused practice.</t>
@@ -4436,8 +4331,6 @@
       <c r="G30" t="n">
         <v>0</v>
       </c>
-      <c r="H30" t="inlineStr"/>
-      <c r="I30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -4570,7 +4463,6 @@
       <c r="G2" t="n">
         <v>0</v>
       </c>
-      <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr">
         <is>
           <t>Consistently excellent — ready for tougher challenges.</t>
@@ -4601,7 +4493,6 @@
       <c r="G3" t="n">
         <v>0</v>
       </c>
-      <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr">
         <is>
           <t>Strong performer, small gains possible with more practice.</t>
@@ -4807,7 +4698,6 @@
       <c r="G9" t="n">
         <v>0</v>
       </c>
-      <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr">
         <is>
           <t>Great turnaround this term, keep the momentum going!</t>
@@ -5398,7 +5288,6 @@
       <c r="G26" t="n">
         <v>0</v>
       </c>
-      <c r="H26" t="inlineStr"/>
       <c r="I26" t="inlineStr">
         <is>
           <t>Exceptional performance, keep up this standard.</t>
@@ -5499,7 +5388,6 @@
       <c r="G29" t="n">
         <v>0</v>
       </c>
-      <c r="H29" t="inlineStr"/>
       <c r="I29" t="inlineStr">
         <is>
           <t>Average performance — revision of basics recommended.</t>
@@ -5530,7 +5418,6 @@
       <c r="G30" t="n">
         <v>0</v>
       </c>
-      <c r="H30" t="inlineStr"/>
       <c r="I30" t="inlineStr">
         <is>
           <t>On track, but should aim higher with focused practice.</t>
@@ -5561,7 +5448,6 @@
       <c r="G31" t="n">
         <v>0</v>
       </c>
-      <c r="H31" t="inlineStr"/>
       <c r="I31" t="inlineStr">
         <is>
           <t>Struggling with fundamentals, needs remedial sessions.</t>
